--- a/doc/modbus_register.xlsx
+++ b/doc/modbus_register.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="12420"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>寄存器地址</t>
   </si>
@@ -52,13 +52,7 @@
     <t>grind_data_lsb</t>
   </si>
   <si>
-    <t>研磨数据低位(时间ms/重量g)</t>
-  </si>
-  <si>
-    <t>grind_data_msb</t>
-  </si>
-  <si>
-    <t>研磨数据高位</t>
+    <t>研磨数据(时间ms/重量g)</t>
   </si>
   <si>
     <t>step_motor_running</t>
@@ -70,13 +64,7 @@
     <t>step_data_lsb</t>
   </si>
   <si>
-    <t>步进电机数据低位(时间ms)</t>
-  </si>
-  <si>
-    <t>step_data_msb</t>
-  </si>
-  <si>
-    <t>步进电机数据高位</t>
+    <t>步进电机数据(时间ms)</t>
   </si>
   <si>
     <t>保持寄存器（Holding Register）</t>
@@ -1078,7 +1066,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="37.2222222222222" customWidth="1"/>
@@ -1147,36 +1135,36 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2">
-        <v>30005</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2">
+        <v>40001</v>
+      </c>
+      <c r="B11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2">
-        <v>30006</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C11" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2">
+        <v>40002</v>
+      </c>
+      <c r="B12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
+      <c r="C12" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2">
-        <v>40001</v>
+        <v>40003</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1187,7 +1175,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2">
-        <v>40002</v>
+        <v>40004</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
@@ -1198,7 +1186,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2">
-        <v>40003</v>
+        <v>40005</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
@@ -1209,7 +1197,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2">
-        <v>40004</v>
+        <v>40006</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
@@ -1220,7 +1208,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2">
-        <v>40005</v>
+        <v>40007</v>
       </c>
       <c r="B17" t="s">
         <v>25</v>
@@ -1231,7 +1219,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2">
-        <v>40006</v>
+        <v>40008</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -1242,35 +1230,13 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2">
-        <v>40007</v>
+        <v>40009</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2">
-        <v>40008</v>
-      </c>
-      <c r="B20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2">
-        <v>40009</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/doc/modbus_register.xlsx
+++ b/doc/modbus_register.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1067,10 +1067,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="37.2222222222222" customWidth="1"/>
-    <col min="2" max="2" width="35.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="37.225" customWidth="1"/>
+    <col min="2" max="2" width="35.775" customWidth="1"/>
     <col min="3" max="3" width="29.3333333333333" customWidth="1"/>
     <col min="4" max="4" width="18.6666666666667" customWidth="1"/>
   </cols>
@@ -1250,7 +1250,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1262,7 +1262,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/doc/modbus_register.xlsx
+++ b/doc/modbus_register.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>寄存器地址</t>
   </si>
@@ -122,6 +122,12 @@
   </si>
   <si>
     <t>运行时间 ms</t>
+  </si>
+  <si>
+    <t>grind_calibration</t>
+  </si>
+  <si>
+    <t>校准</t>
   </si>
 </sst>
 </file>
@@ -1066,7 +1072,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="37.225" customWidth="1"/>
@@ -1237,6 +1243,17 @@
       </c>
       <c r="C19" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2">
+        <v>40010</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/doc/modbus_register.xlsx
+++ b/doc/modbus_register.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>寄存器地址</t>
   </si>
@@ -128,6 +128,12 @@
   </si>
   <si>
     <t>校准</t>
+  </si>
+  <si>
+    <t>grind_speed</t>
+  </si>
+  <si>
+    <t>磨豆速度</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="37.225" customWidth="1"/>
@@ -1254,6 +1260,17 @@
       </c>
       <c r="C20" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2">
+        <v>40011</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
